--- a/ttl_long/AdHoc_Net_15.xlsx
+++ b/ttl_long/AdHoc_Net_15.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>236</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>37</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>215</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>234</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>157</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>260</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>244</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>275</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>329</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>264</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>439</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>442</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>369</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>102</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>461</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>503</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>562</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>600</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>247</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>654</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>866</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>169</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>786</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>807</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1003</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>965</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>966</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>980</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1050</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1071</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1265</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>164</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1166</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,148 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1247</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1568</t>
         </is>
       </c>
     </row>
@@ -956,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,7 +1125,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1011,7 +1147,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1033,7 +1169,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1055,7 +1191,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1077,7 +1213,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,7 +1257,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1187,7 +1323,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,7 +1345,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1248,12 +1384,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1275,7 +1411,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1292,12 +1428,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1319,7 +1455,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1358,7 +1494,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1380,12 +1516,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1407,7 +1543,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1424,12 +1560,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1446,12 +1582,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,12 +1604,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1490,7 +1626,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1517,7 +1653,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1534,12 +1670,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1561,7 +1697,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1583,7 +1719,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1600,12 +1736,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1627,7 +1763,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1649,7 +1785,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1693,7 +1829,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1715,7 +1851,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1732,12 +1868,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1759,7 +1895,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1776,12 +1912,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1798,12 +1934,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1825,7 +1961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1847,7 +1983,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1864,12 +2000,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1891,7 +2027,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1913,7 +2049,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1935,7 +2071,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1974,7 +2110,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2001,7 +2137,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2023,7 +2159,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2067,7 +2203,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2089,7 +2225,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2150,12 +2286,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2177,7 +2313,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2194,12 +2330,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2216,12 +2352,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2238,12 +2374,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2260,12 +2396,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2287,7 +2423,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2304,12 +2440,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2326,12 +2462,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2348,12 +2484,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2370,12 +2506,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2392,12 +2528,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2414,12 +2550,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2436,7 +2572,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2458,12 +2594,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2480,12 +2616,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2502,12 +2638,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2524,12 +2660,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2546,12 +2682,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2568,7 +2704,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2590,12 +2726,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2612,12 +2748,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2634,20 +2770,636 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2686,7 +3438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2696,7 +3448,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -2722,7 +3474,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_15.xlsx
+++ b/ttl_long/AdHoc_Net_15.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>304</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>320</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>324</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>227</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>386</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>291</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>378</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>564</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>426</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>316</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>491</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>271</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>568</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>611</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>715</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>788</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>789</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>905</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>892</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>873</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1054</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>975</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1022</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1085</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>186</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1199</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1159</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1202</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1166</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1252</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1446</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1332</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1339</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1528</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,63 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1512</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1588</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1695</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1169,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1186,7 +1237,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1213,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1235,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1252,12 +1303,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1279,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1301,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1323,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1345,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1362,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1384,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1406,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1433,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1450,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1472,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1521,7 +1572,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1538,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1565,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1582,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1604,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1626,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1648,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1670,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1692,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1714,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1741,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1758,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1780,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1802,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1829,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1846,7 +1897,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1873,7 +1924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1895,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1912,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1939,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1961,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1983,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2005,7 +2056,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2027,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2044,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2071,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2093,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2115,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2137,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2154,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2181,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2225,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2247,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2269,7 +2320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2286,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2335,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2352,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2379,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2401,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2423,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2445,7 +2496,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2467,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2489,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2511,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2533,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2550,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2572,7 +2623,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2594,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2616,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2638,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2660,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2682,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2704,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2726,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2748,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2770,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2792,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2836,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2858,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2880,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2902,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2924,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2973,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2995,7 +3046,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3039,7 +3090,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3056,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3083,7 +3134,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3105,7 +3156,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3122,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3144,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3166,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3188,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3215,7 +3266,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3232,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3254,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3276,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3298,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3320,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3342,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3364,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3391,15 +3442,169 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3438,7 +3643,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3448,7 +3653,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -3468,7 +3673,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_15.xlsx
+++ b/ttl_long/AdHoc_Net_15.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>277</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>268</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>180</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>300</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>316</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>376</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>404</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>522</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>565</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>493</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>608</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>163</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>642</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>581</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>782</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>265</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>681</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>772</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>851</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>908</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>320</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>868</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>971</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>983</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>337</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>980</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1056</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>118</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1128</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1088</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1238</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1225</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1224</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1390</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1312</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1392</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1508</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1493</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>1522</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1650</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1631</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1303,12 +1303,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1325,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1413,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2337,7 +2337,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2711,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3107,12 +3107,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3195,7 +3195,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,7 +3371,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,7 +3547,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3561,50 +3561,6 @@
         </is>
       </c>
       <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3643,7 +3599,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -3653,7 +3609,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
